--- a/Results/Study 2/GoogLeNet (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 2/GoogLeNet (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>489</v>
+        <v>405</v>
       </c>
       <c r="C2">
-        <v>151</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>214</v>
+        <v>291</v>
       </c>
       <c r="C3">
-        <v>426</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C2">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C3">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Study 2/GoogLeNet (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 2/GoogLeNet (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C2">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:3">

--- a/Results/Study 2/GoogLeNet (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 2/GoogLeNet (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="C2">
-        <v>234</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="C3">
-        <v>349</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C2">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C3">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
